--- a/lab-standards/BJMA-lab-standard.xlsx
+++ b/lab-standards/BJMA-lab-standard.xlsx
@@ -700,7 +700,9 @@
       <c r="C16" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="31" t="n"/>
+      <c r="D16" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="31" t="n">
         <v>5</v>
       </c>
@@ -722,7 +724,9 @@
       <c r="C17" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="31" t="n"/>
+      <c r="D17" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="31" t="n">
         <v>5</v>
       </c>
@@ -744,7 +748,9 @@
       <c r="C18" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="31" t="n"/>
+      <c r="D18" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="31" t="n">
         <v>5</v>
       </c>
@@ -766,7 +772,9 @@
       <c r="C19" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="31" t="n"/>
+      <c r="D19" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="31" t="n">
         <v>5</v>
       </c>
@@ -788,7 +796,9 @@
       <c r="C20" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="31" t="n"/>
+      <c r="D20" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="31" t="n">
         <v>9</v>
       </c>
@@ -810,7 +820,9 @@
       <c r="C21" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="31" t="n"/>
+      <c r="D21" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="31" t="n">
         <v>9</v>
       </c>
@@ -832,7 +844,9 @@
       <c r="C22" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="31" t="n"/>
+      <c r="D22" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="31" t="n">
         <v>5</v>
       </c>
@@ -854,7 +868,9 @@
       <c r="C23" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="31" t="n"/>
+      <c r="D23" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="31" t="n">
         <v>6</v>
       </c>
@@ -876,7 +892,9 @@
       <c r="C24" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="31" t="n"/>
+      <c r="D24" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="31" t="n">
         <v>4</v>
       </c>
@@ -898,7 +916,9 @@
       <c r="C25" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="D25" s="31" t="n"/>
+      <c r="D25" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="31" t="n">
         <v>7</v>
       </c>
@@ -920,7 +940,9 @@
       <c r="C26" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="D26" s="31" t="n"/>
+      <c r="D26" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="31" t="n">
         <v>7</v>
       </c>
@@ -942,7 +964,9 @@
       <c r="C27" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="D27" s="31" t="n"/>
+      <c r="D27" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="31" t="n">
         <v>4</v>
       </c>
@@ -964,7 +988,9 @@
       <c r="C28" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="31" t="n"/>
+      <c r="D28" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="31" t="n">
         <v>7</v>
       </c>
@@ -986,7 +1012,9 @@
       <c r="C29" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="31" t="n"/>
+      <c r="D29" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="31" t="n">
         <v>5</v>
       </c>
@@ -1008,7 +1036,9 @@
       <c r="C30" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="31" t="n"/>
+      <c r="D30" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="31" t="n">
         <v>8</v>
       </c>
@@ -1030,7 +1060,9 @@
       <c r="C31" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="31" t="n"/>
+      <c r="D31" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="31" t="n">
         <v>6</v>
       </c>
@@ -1052,7 +1084,9 @@
       <c r="C32" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="D32" s="31" t="n"/>
+      <c r="D32" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="31" t="n">
         <v>5</v>
       </c>
@@ -1074,7 +1108,9 @@
       <c r="C33" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="31" t="n"/>
+      <c r="D33" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="31" t="n">
         <v>7</v>
       </c>
@@ -1096,7 +1132,9 @@
       <c r="C34" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="31" t="n"/>
+      <c r="D34" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="31" t="n">
         <v>9</v>
       </c>
@@ -1118,7 +1156,9 @@
       <c r="C35" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="31" t="n"/>
+      <c r="D35" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="31" t="n">
         <v>6</v>
       </c>
@@ -1140,7 +1180,9 @@
       <c r="C36" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D36" s="31" t="n"/>
+      <c r="D36" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="31" t="n">
         <v>5</v>
       </c>
@@ -1162,7 +1204,9 @@
       <c r="C37" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="31" t="n"/>
+      <c r="D37" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="31" t="n">
         <v>4</v>
       </c>
@@ -1184,7 +1228,9 @@
       <c r="C38" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="31" t="n"/>
+      <c r="D38" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="31" t="n">
         <v>5</v>
       </c>
@@ -1206,7 +1252,9 @@
       <c r="C39" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D39" s="31" t="n"/>
+      <c r="D39" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="31" t="n">
         <v>4</v>
       </c>
@@ -1228,7 +1276,9 @@
       <c r="C40" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D40" s="31" t="n"/>
+      <c r="D40" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="31" t="n">
         <v>4</v>
       </c>
@@ -1466,7 +1516,9 @@
       <c r="C16" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="31" t="n"/>
+      <c r="D16" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="31" t="n">
         <v>5</v>
       </c>
@@ -1488,7 +1540,9 @@
       <c r="C17" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="31" t="n"/>
+      <c r="D17" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="31" t="n">
         <v>5</v>
       </c>
@@ -1510,7 +1564,9 @@
       <c r="C18" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="31" t="n"/>
+      <c r="D18" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="31" t="n">
         <v>5</v>
       </c>
@@ -1532,7 +1588,9 @@
       <c r="C19" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="31" t="n"/>
+      <c r="D19" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="31" t="n">
         <v>4</v>
       </c>
@@ -1554,7 +1612,9 @@
       <c r="C20" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="31" t="n"/>
+      <c r="D20" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="31" t="n">
         <v>10</v>
       </c>
@@ -1576,7 +1636,9 @@
       <c r="C21" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="31" t="n"/>
+      <c r="D21" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="31" t="n">
         <v>9</v>
       </c>
@@ -1598,7 +1660,9 @@
       <c r="C22" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="31" t="n"/>
+      <c r="D22" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="31" t="n">
         <v>9</v>
       </c>
@@ -1620,7 +1684,9 @@
       <c r="C23" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="31" t="n"/>
+      <c r="D23" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="31" t="n">
         <v>9</v>
       </c>
@@ -1642,7 +1708,9 @@
       <c r="C24" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="D24" s="31" t="n"/>
+      <c r="D24" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="31" t="n">
         <v>6</v>
       </c>
@@ -1664,7 +1732,9 @@
       <c r="C25" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="31" t="n"/>
+      <c r="D25" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="31" t="n">
         <v>6</v>
       </c>
@@ -1686,7 +1756,9 @@
       <c r="C26" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="31" t="n"/>
+      <c r="D26" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="31" t="n">
         <v>6</v>
       </c>
@@ -1708,7 +1780,9 @@
       <c r="C27" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="31" t="n"/>
+      <c r="D27" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="31" t="n">
         <v>4</v>
       </c>
@@ -1730,7 +1804,9 @@
       <c r="C28" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="31" t="n"/>
+      <c r="D28" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="31" t="n">
         <v>4</v>
       </c>
@@ -1752,7 +1828,9 @@
       <c r="C29" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="31" t="n"/>
+      <c r="D29" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="31" t="n">
         <v>3</v>
       </c>
@@ -1774,7 +1852,9 @@
       <c r="C30" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D30" s="31" t="n"/>
+      <c r="D30" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="31" t="n">
         <v>6</v>
       </c>
@@ -1796,7 +1876,9 @@
       <c r="C31" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="31" t="n"/>
+      <c r="D31" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="31" t="n">
         <v>6</v>
       </c>
@@ -1818,7 +1900,9 @@
       <c r="C32" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="31" t="n"/>
+      <c r="D32" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="31" t="n">
         <v>7</v>
       </c>
@@ -1840,7 +1924,9 @@
       <c r="C33" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="D33" s="31" t="n"/>
+      <c r="D33" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="31" t="n">
         <v>5</v>
       </c>
@@ -1862,7 +1948,9 @@
       <c r="C34" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="D34" s="31" t="n"/>
+      <c r="D34" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="31" t="n">
         <v>4</v>
       </c>
@@ -1884,7 +1972,9 @@
       <c r="C35" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="D35" s="31" t="n"/>
+      <c r="D35" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="31" t="n">
         <v>3</v>
       </c>
@@ -2125,7 +2215,9 @@
       <c r="C16" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="31" t="n"/>
+      <c r="D16" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="31" t="n">
         <v>5</v>
       </c>
@@ -2147,7 +2239,9 @@
       <c r="C17" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="31" t="n"/>
+      <c r="D17" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="31" t="n">
         <v>5</v>
       </c>
@@ -2169,7 +2263,9 @@
       <c r="C18" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="31" t="n"/>
+      <c r="D18" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="31" t="n">
         <v>5</v>
       </c>
@@ -2191,7 +2287,9 @@
       <c r="C19" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="31" t="n"/>
+      <c r="D19" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="31" t="n">
         <v>5</v>
       </c>
@@ -2213,7 +2311,9 @@
       <c r="C20" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="31" t="n"/>
+      <c r="D20" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="31" t="n">
         <v>5</v>
       </c>
@@ -2235,7 +2335,9 @@
       <c r="C21" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="31" t="n"/>
+      <c r="D21" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="31" t="n">
         <v>4</v>
       </c>
@@ -2257,7 +2359,9 @@
       <c r="C22" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="31" t="n"/>
+      <c r="D22" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="31" t="n">
         <v>6</v>
       </c>
@@ -2279,7 +2383,9 @@
       <c r="C23" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="31" t="n"/>
+      <c r="D23" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="31" t="n">
         <v>6</v>
       </c>
@@ -2301,7 +2407,9 @@
       <c r="C24" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="31" t="n"/>
+      <c r="D24" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="31" t="n">
         <v>5</v>
       </c>
@@ -2323,7 +2431,9 @@
       <c r="C25" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="31" t="n"/>
+      <c r="D25" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="31" t="n">
         <v>5</v>
       </c>
@@ -2345,7 +2455,9 @@
       <c r="C26" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="31" t="n"/>
+      <c r="D26" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="31" t="n">
         <v>3</v>
       </c>
@@ -2367,7 +2479,9 @@
       <c r="C27" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="31" t="n"/>
+      <c r="D27" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="31" t="n">
         <v>6</v>
       </c>
@@ -2389,7 +2503,9 @@
       <c r="C28" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="31" t="n"/>
+      <c r="D28" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="31" t="n">
         <v>6</v>
       </c>
@@ -2627,7 +2743,9 @@
       <c r="C16" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="31" t="n"/>
+      <c r="D16" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="31" t="n">
         <v>5</v>
       </c>
@@ -2649,7 +2767,9 @@
       <c r="C17" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="31" t="n"/>
+      <c r="D17" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="31" t="n">
         <v>5</v>
       </c>
@@ -2671,7 +2791,9 @@
       <c r="C18" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="31" t="n"/>
+      <c r="D18" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="31" t="n">
         <v>5</v>
       </c>
@@ -2693,7 +2815,9 @@
       <c r="C19" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="31" t="n"/>
+      <c r="D19" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="31" t="n">
         <v>3</v>
       </c>
@@ -2715,7 +2839,9 @@
       <c r="C20" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="31" t="n"/>
+      <c r="D20" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="31" t="n">
         <v>3</v>
       </c>
@@ -2737,7 +2863,9 @@
       <c r="C21" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="31" t="n"/>
+      <c r="D21" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="31" t="n">
         <v>5</v>
       </c>
@@ -2759,7 +2887,9 @@
       <c r="C22" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="31" t="n"/>
+      <c r="D22" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="31" t="n">
         <v>5</v>
       </c>
@@ -2781,7 +2911,9 @@
       <c r="C23" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="31" t="n"/>
+      <c r="D23" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="31" t="n">
         <v>6</v>
       </c>
@@ -2803,7 +2935,9 @@
       <c r="C24" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="31" t="n"/>
+      <c r="D24" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="31" t="n">
         <v>6</v>
       </c>
@@ -2825,7 +2959,9 @@
       <c r="C25" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="31" t="n"/>
+      <c r="D25" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="31" t="n">
         <v>6</v>
       </c>
@@ -2847,7 +2983,9 @@
       <c r="C26" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="31" t="n"/>
+      <c r="D26" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="31" t="n">
         <v>6</v>
       </c>
@@ -2869,7 +3007,9 @@
       <c r="C27" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="31" t="n"/>
+      <c r="D27" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="31" t="n">
         <v>9</v>
       </c>
@@ -2891,7 +3031,9 @@
       <c r="C28" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="31" t="n"/>
+      <c r="D28" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="31" t="n">
         <v>9</v>
       </c>
@@ -2913,7 +3055,9 @@
       <c r="C29" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="31" t="n"/>
+      <c r="D29" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="31" t="n">
         <v>9</v>
       </c>
@@ -2935,7 +3079,9 @@
       <c r="C30" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="31" t="n"/>
+      <c r="D30" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="31" t="n">
         <v>10</v>
       </c>
@@ -2957,7 +3103,9 @@
       <c r="C31" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="31" t="n"/>
+      <c r="D31" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="31" t="n">
         <v>9</v>
       </c>
@@ -2979,7 +3127,9 @@
       <c r="C32" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="31" t="n"/>
+      <c r="D32" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="31" t="n">
         <v>9</v>
       </c>
@@ -3001,7 +3151,9 @@
       <c r="C33" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="31" t="n"/>
+      <c r="D33" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="31" t="n">
         <v>10</v>
       </c>
@@ -3023,7 +3175,9 @@
       <c r="C34" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="31" t="n"/>
+      <c r="D34" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="31" t="n">
         <v>7</v>
       </c>
@@ -3045,7 +3199,9 @@
       <c r="C35" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="31" t="n"/>
+      <c r="D35" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="31" t="n">
         <v>8</v>
       </c>
@@ -3067,7 +3223,9 @@
       <c r="C36" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="31" t="n"/>
+      <c r="D36" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="31" t="n">
         <v>6</v>
       </c>
@@ -3089,7 +3247,9 @@
       <c r="C37" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="31" t="n"/>
+      <c r="D37" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="31" t="n">
         <v>8</v>
       </c>
@@ -3111,7 +3271,9 @@
       <c r="C38" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="31" t="n"/>
+      <c r="D38" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="31" t="n">
         <v>7</v>
       </c>
@@ -3133,7 +3295,9 @@
       <c r="C39" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="31" t="n"/>
+      <c r="D39" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="31" t="n">
         <v>3</v>
       </c>
@@ -3155,7 +3319,9 @@
       <c r="C40" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D40" s="31" t="n"/>
+      <c r="D40" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="31" t="n">
         <v>5</v>
       </c>
@@ -3177,7 +3343,9 @@
       <c r="C41" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="31" t="n"/>
+      <c r="D41" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="31" t="n">
         <v>5</v>
       </c>
@@ -3199,7 +3367,9 @@
       <c r="C42" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D42" s="31" t="n"/>
+      <c r="D42" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="31" t="n">
         <v>5</v>
       </c>
@@ -3221,7 +3391,9 @@
       <c r="C43" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D43" s="31" t="n"/>
+      <c r="D43" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" s="31" t="n">
         <v>4</v>
       </c>
@@ -3243,7 +3415,9 @@
       <c r="C44" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="31" t="n"/>
+      <c r="D44" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E44" s="31" t="n">
         <v>4</v>
       </c>
@@ -3265,7 +3439,9 @@
       <c r="C45" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D45" s="31" t="n"/>
+      <c r="D45" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E45" s="31" t="n">
         <v>4</v>
       </c>
@@ -3287,7 +3463,9 @@
       <c r="C46" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D46" s="31" t="n"/>
+      <c r="D46" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E46" s="31" t="n">
         <v>3</v>
       </c>
@@ -3309,7 +3487,9 @@
       <c r="C47" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D47" s="31" t="n"/>
+      <c r="D47" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E47" s="31" t="n">
         <v>3</v>
       </c>
@@ -3547,7 +3727,9 @@
       <c r="C16" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="D16" s="31" t="n"/>
+      <c r="D16" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="31" t="n">
         <v>5</v>
       </c>
@@ -3569,7 +3751,9 @@
       <c r="C17" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="31" t="n"/>
+      <c r="D17" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="31" t="n">
         <v>5</v>
       </c>
@@ -3591,7 +3775,9 @@
       <c r="C18" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="31" t="n"/>
+      <c r="D18" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="31" t="n">
         <v>5</v>
       </c>
@@ -3613,7 +3799,9 @@
       <c r="C19" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="31" t="n"/>
+      <c r="D19" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="31" t="n">
         <v>3</v>
       </c>
@@ -3635,7 +3823,9 @@
       <c r="C20" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="31" t="n"/>
+      <c r="D20" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="31" t="n">
         <v>3</v>
       </c>
@@ -3657,7 +3847,9 @@
       <c r="C21" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="31" t="n"/>
+      <c r="D21" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="31" t="n">
         <v>5</v>
       </c>
@@ -3679,7 +3871,9 @@
       <c r="C22" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="31" t="n"/>
+      <c r="D22" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="31" t="n">
         <v>5</v>
       </c>
@@ -3701,7 +3895,9 @@
       <c r="C23" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="31" t="n"/>
+      <c r="D23" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="31" t="n">
         <v>8</v>
       </c>
@@ -3723,7 +3919,9 @@
       <c r="C24" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="31" t="n"/>
+      <c r="D24" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="31" t="n">
         <v>6</v>
       </c>
@@ -3745,7 +3943,9 @@
       <c r="C25" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="31" t="n"/>
+      <c r="D25" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="31" t="n">
         <v>6</v>
       </c>
@@ -3767,7 +3967,9 @@
       <c r="C26" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="31" t="n"/>
+      <c r="D26" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="31" t="n">
         <v>6</v>
       </c>
@@ -3789,7 +3991,9 @@
       <c r="C27" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="31" t="n"/>
+      <c r="D27" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="31" t="n">
         <v>6</v>
       </c>
@@ -3811,7 +4015,9 @@
       <c r="C28" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="31" t="n"/>
+      <c r="D28" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="31" t="n">
         <v>7</v>
       </c>
@@ -3833,7 +4039,9 @@
       <c r="C29" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="31" t="n"/>
+      <c r="D29" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="31" t="n">
         <v>7</v>
       </c>
@@ -3855,7 +4063,9 @@
       <c r="C30" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="31" t="n"/>
+      <c r="D30" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="31" t="n">
         <v>5</v>
       </c>
@@ -3877,7 +4087,9 @@
       <c r="C31" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D31" s="31" t="n"/>
+      <c r="D31" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="31" t="n">
         <v>7</v>
       </c>
@@ -3899,7 +4111,9 @@
       <c r="C32" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="D32" s="31" t="n"/>
+      <c r="D32" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="31" t="n">
         <v>3</v>
       </c>
@@ -3921,7 +4135,9 @@
       <c r="C33" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="D33" s="31" t="n"/>
+      <c r="D33" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="31" t="n">
         <v>3</v>
       </c>
@@ -3943,7 +4159,9 @@
       <c r="C34" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="D34" s="31" t="n"/>
+      <c r="D34" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="31" t="n">
         <v>3</v>
       </c>
@@ -3965,7 +4183,9 @@
       <c r="C35" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="D35" s="31" t="n"/>
+      <c r="D35" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="31" t="n">
         <v>3</v>
       </c>
@@ -3987,7 +4207,9 @@
       <c r="C36" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D36" s="31" t="n"/>
+      <c r="D36" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="31" t="n">
         <v>4</v>
       </c>
@@ -4009,7 +4231,9 @@
       <c r="C37" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="D37" s="31" t="n"/>
+      <c r="D37" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="31" t="n">
         <v>6</v>
       </c>
@@ -4031,7 +4255,9 @@
       <c r="C38" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="31" t="n"/>
+      <c r="D38" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="31" t="n">
         <v>3</v>
       </c>
@@ -4053,7 +4279,9 @@
       <c r="C39" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="31" t="n"/>
+      <c r="D39" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="31" t="n">
         <v>4</v>
       </c>
@@ -4075,7 +4303,9 @@
       <c r="C40" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="D40" s="31" t="n"/>
+      <c r="D40" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="31" t="n">
         <v>3</v>
       </c>
@@ -4097,7 +4327,9 @@
       <c r="C41" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="31" t="n"/>
+      <c r="D41" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="31" t="n">
         <v>5</v>
       </c>
@@ -4119,7 +4351,9 @@
       <c r="C42" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="D42" s="31" t="n"/>
+      <c r="D42" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="31" t="n">
         <v>3</v>
       </c>
@@ -4141,7 +4375,9 @@
       <c r="C43" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="D43" s="31" t="n"/>
+      <c r="D43" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" s="31" t="n">
         <v>3</v>
       </c>
@@ -4163,7 +4399,9 @@
       <c r="C44" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="31" t="n"/>
+      <c r="D44" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E44" s="31" t="n">
         <v>7</v>
       </c>
@@ -4185,7 +4423,9 @@
       <c r="C45" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D45" s="31" t="n"/>
+      <c r="D45" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E45" s="31" t="n">
         <v>5</v>
       </c>
@@ -4207,7 +4447,9 @@
       <c r="C46" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D46" s="31" t="n"/>
+      <c r="D46" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E46" s="31" t="n">
         <v>8</v>
       </c>
@@ -4229,7 +4471,9 @@
       <c r="C47" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D47" s="31" t="n"/>
+      <c r="D47" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E47" s="31" t="n">
         <v>4</v>
       </c>
@@ -4251,7 +4495,9 @@
       <c r="C48" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D48" s="31" t="n"/>
+      <c r="D48" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E48" s="31" t="n">
         <v>3</v>
       </c>
@@ -4273,7 +4519,9 @@
       <c r="C49" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D49" s="31" t="n"/>
+      <c r="D49" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E49" s="31" t="n">
         <v>3</v>
       </c>
@@ -4511,7 +4759,9 @@
       <c r="C16" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="D16" s="31" t="n"/>
+      <c r="D16" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="31" t="n">
         <v>5</v>
       </c>
@@ -4533,7 +4783,9 @@
       <c r="C17" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="31" t="n"/>
+      <c r="D17" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="31" t="n">
         <v>5</v>
       </c>
@@ -4555,7 +4807,9 @@
       <c r="C18" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="31" t="n"/>
+      <c r="D18" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="31" t="n">
         <v>5</v>
       </c>
@@ -4577,7 +4831,9 @@
       <c r="C19" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="31" t="n"/>
+      <c r="D19" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="31" t="n">
         <v>3</v>
       </c>
@@ -4599,7 +4855,9 @@
       <c r="C20" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="31" t="n"/>
+      <c r="D20" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="31" t="n">
         <v>3</v>
       </c>
@@ -4621,7 +4879,9 @@
       <c r="C21" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="31" t="n"/>
+      <c r="D21" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="31" t="n">
         <v>5</v>
       </c>
@@ -4643,7 +4903,9 @@
       <c r="C22" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="31" t="n"/>
+      <c r="D22" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="31" t="n">
         <v>5</v>
       </c>
@@ -4665,7 +4927,9 @@
       <c r="C23" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="31" t="n"/>
+      <c r="D23" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="31" t="n">
         <v>6</v>
       </c>
@@ -4687,7 +4951,9 @@
       <c r="C24" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="31" t="n"/>
+      <c r="D24" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="31" t="n">
         <v>6</v>
       </c>
@@ -4709,7 +4975,9 @@
       <c r="C25" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="31" t="n"/>
+      <c r="D25" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="31" t="n">
         <v>6</v>
       </c>
@@ -4731,7 +4999,9 @@
       <c r="C26" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="31" t="n"/>
+      <c r="D26" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="31" t="n">
         <v>6</v>
       </c>
@@ -4753,7 +5023,9 @@
       <c r="C27" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="31" t="n"/>
+      <c r="D27" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="31" t="n">
         <v>7</v>
       </c>
@@ -4775,7 +5047,9 @@
       <c r="C28" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="31" t="n"/>
+      <c r="D28" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="31" t="n">
         <v>7</v>
       </c>
@@ -4797,7 +5071,9 @@
       <c r="C29" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="31" t="n"/>
+      <c r="D29" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="31" t="n">
         <v>5</v>
       </c>
@@ -4819,7 +5095,9 @@
       <c r="C30" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D30" s="31" t="n"/>
+      <c r="D30" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="31" t="n">
         <v>7</v>
       </c>
@@ -4841,7 +5119,9 @@
       <c r="C31" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="D31" s="31" t="n"/>
+      <c r="D31" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="31" t="n">
         <v>3</v>
       </c>
@@ -4863,7 +5143,9 @@
       <c r="C32" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="D32" s="31" t="n"/>
+      <c r="D32" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="31" t="n">
         <v>3</v>
       </c>
@@ -4885,7 +5167,9 @@
       <c r="C33" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="D33" s="31" t="n"/>
+      <c r="D33" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="31" t="n">
         <v>3</v>
       </c>
@@ -4907,7 +5191,9 @@
       <c r="C34" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="D34" s="31" t="n"/>
+      <c r="D34" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="31" t="n">
         <v>3</v>
       </c>
@@ -4929,7 +5215,9 @@
       <c r="C35" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="31" t="n"/>
+      <c r="D35" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="31" t="n">
         <v>4</v>
       </c>
@@ -4951,7 +5239,9 @@
       <c r="C36" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="D36" s="31" t="n"/>
+      <c r="D36" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="31" t="n">
         <v>8</v>
       </c>
@@ -4973,7 +5263,9 @@
       <c r="C37" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D37" s="31" t="n"/>
+      <c r="D37" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="31" t="n">
         <v>3</v>
       </c>
@@ -4995,7 +5287,9 @@
       <c r="C38" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="31" t="n"/>
+      <c r="D38" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="31" t="n">
         <v>5</v>
       </c>
@@ -5017,7 +5311,9 @@
       <c r="C39" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="D39" s="31" t="n"/>
+      <c r="D39" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="31" t="n">
         <v>3</v>
       </c>
@@ -5039,7 +5335,9 @@
       <c r="C40" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D40" s="31" t="n"/>
+      <c r="D40" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="31" t="n">
         <v>5</v>
       </c>
@@ -5061,7 +5359,9 @@
       <c r="C41" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="D41" s="31" t="n"/>
+      <c r="D41" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="31" t="n">
         <v>3</v>
       </c>
@@ -5083,7 +5383,9 @@
       <c r="C42" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="D42" s="31" t="n"/>
+      <c r="D42" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="31" t="n">
         <v>3</v>
       </c>
@@ -5105,7 +5407,9 @@
       <c r="C43" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D43" s="31" t="n"/>
+      <c r="D43" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" s="31" t="n">
         <v>8</v>
       </c>
@@ -5127,7 +5431,9 @@
       <c r="C44" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="31" t="n"/>
+      <c r="D44" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E44" s="31" t="n">
         <v>8</v>
       </c>
@@ -5149,7 +5455,9 @@
       <c r="C45" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D45" s="31" t="n"/>
+      <c r="D45" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E45" s="31" t="n">
         <v>7</v>
       </c>
@@ -5171,7 +5479,9 @@
       <c r="C46" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D46" s="31" t="n"/>
+      <c r="D46" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E46" s="31" t="n">
         <v>5</v>
       </c>
@@ -5193,7 +5503,9 @@
       <c r="C47" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D47" s="31" t="n"/>
+      <c r="D47" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E47" s="31" t="n">
         <v>3</v>
       </c>
@@ -5215,7 +5527,9 @@
       <c r="C48" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D48" s="31" t="n"/>
+      <c r="D48" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E48" s="31" t="n">
         <v>3</v>
       </c>
@@ -5453,7 +5767,9 @@
       <c r="C16" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="D16" s="31" t="n"/>
+      <c r="D16" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="31" t="n">
         <v>5</v>
       </c>
@@ -5475,7 +5791,9 @@
       <c r="C17" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="31" t="n"/>
+      <c r="D17" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="31" t="n">
         <v>5</v>
       </c>
@@ -5497,7 +5815,9 @@
       <c r="C18" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="31" t="n"/>
+      <c r="D18" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="31" t="n">
         <v>5</v>
       </c>
@@ -5519,7 +5839,9 @@
       <c r="C19" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="31" t="n"/>
+      <c r="D19" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="31" t="n">
         <v>3</v>
       </c>
@@ -5541,7 +5863,9 @@
       <c r="C20" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="31" t="n"/>
+      <c r="D20" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="31" t="n">
         <v>3</v>
       </c>
@@ -5563,7 +5887,9 @@
       <c r="C21" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="31" t="n"/>
+      <c r="D21" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="31" t="n">
         <v>5</v>
       </c>
@@ -5585,7 +5911,9 @@
       <c r="C22" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="31" t="n"/>
+      <c r="D22" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="31" t="n">
         <v>5</v>
       </c>
@@ -5607,7 +5935,9 @@
       <c r="C23" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="31" t="n"/>
+      <c r="D23" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="31" t="n">
         <v>6</v>
       </c>
@@ -5629,7 +5959,9 @@
       <c r="C24" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="31" t="n"/>
+      <c r="D24" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="31" t="n">
         <v>6</v>
       </c>
@@ -5651,7 +5983,9 @@
       <c r="C25" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="31" t="n"/>
+      <c r="D25" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="31" t="n">
         <v>6</v>
       </c>
@@ -5673,7 +6007,9 @@
       <c r="C26" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="31" t="n"/>
+      <c r="D26" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="31" t="n">
         <v>6</v>
       </c>
@@ -5695,7 +6031,9 @@
       <c r="C27" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="31" t="n"/>
+      <c r="D27" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="31" t="n">
         <v>6</v>
       </c>
@@ -5717,7 +6055,9 @@
       <c r="C28" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="31" t="n"/>
+      <c r="D28" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="31" t="n">
         <v>6</v>
       </c>
@@ -5739,7 +6079,9 @@
       <c r="C29" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="31" t="n"/>
+      <c r="D29" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="31" t="n">
         <v>6</v>
       </c>
@@ -5761,7 +6103,9 @@
       <c r="C30" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="31" t="n"/>
+      <c r="D30" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="31" t="n">
         <v>6</v>
       </c>
@@ -5783,7 +6127,9 @@
       <c r="C31" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D31" s="31" t="n"/>
+      <c r="D31" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="31" t="n">
         <v>7</v>
       </c>
@@ -5805,7 +6151,9 @@
       <c r="C32" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="31" t="n"/>
+      <c r="D32" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="31" t="n">
         <v>7</v>
       </c>
@@ -5827,7 +6175,9 @@
       <c r="C33" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="31" t="n"/>
+      <c r="D33" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="31" t="n">
         <v>5</v>
       </c>
@@ -5849,7 +6199,9 @@
       <c r="C34" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="31" t="n"/>
+      <c r="D34" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="31" t="n">
         <v>7</v>
       </c>
@@ -5871,7 +6223,9 @@
       <c r="C35" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="D35" s="31" t="n"/>
+      <c r="D35" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="31" t="n">
         <v>3</v>
       </c>
@@ -5893,7 +6247,9 @@
       <c r="C36" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="D36" s="31" t="n"/>
+      <c r="D36" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="31" t="n">
         <v>3</v>
       </c>
@@ -5915,7 +6271,9 @@
       <c r="C37" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="D37" s="31" t="n"/>
+      <c r="D37" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="31" t="n">
         <v>3</v>
       </c>
@@ -5937,7 +6295,9 @@
       <c r="C38" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="D38" s="31" t="n"/>
+      <c r="D38" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="31" t="n">
         <v>3</v>
       </c>
@@ -5959,7 +6319,9 @@
       <c r="C39" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D39" s="31" t="n"/>
+      <c r="D39" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="31" t="n">
         <v>4</v>
       </c>
@@ -5981,7 +6343,9 @@
       <c r="C40" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="D40" s="31" t="n"/>
+      <c r="D40" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="31" t="n">
         <v>6</v>
       </c>
@@ -6003,7 +6367,9 @@
       <c r="C41" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D41" s="31" t="n"/>
+      <c r="D41" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="31" t="n">
         <v>3</v>
       </c>
@@ -6025,7 +6391,9 @@
       <c r="C42" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D42" s="31" t="n"/>
+      <c r="D42" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="31" t="n">
         <v>5</v>
       </c>
@@ -6047,7 +6415,9 @@
       <c r="C43" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="D43" s="31" t="n"/>
+      <c r="D43" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" s="31" t="n">
         <v>3</v>
       </c>
@@ -6069,7 +6439,9 @@
       <c r="C44" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="31" t="n"/>
+      <c r="D44" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E44" s="31" t="n">
         <v>5</v>
       </c>
@@ -6091,7 +6463,9 @@
       <c r="C45" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D45" s="31" t="n"/>
+      <c r="D45" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E45" s="31" t="n">
         <v>4</v>
       </c>
@@ -6113,7 +6487,9 @@
       <c r="C46" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D46" s="31" t="n"/>
+      <c r="D46" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E46" s="31" t="n">
         <v>3</v>
       </c>
@@ -6135,7 +6511,9 @@
       <c r="C47" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D47" s="31" t="n"/>
+      <c r="D47" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E47" s="31" t="n">
         <v>3</v>
       </c>
@@ -6372,7 +6750,9 @@
       <c r="C16" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="31" t="n"/>
+      <c r="D16" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="31" t="n">
         <v>5</v>
       </c>
@@ -6394,7 +6774,9 @@
       <c r="C17" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="31" t="n"/>
+      <c r="D17" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="31" t="n">
         <v>5</v>
       </c>
@@ -6416,7 +6798,9 @@
       <c r="C18" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="31" t="n"/>
+      <c r="D18" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="31" t="n">
         <v>4</v>
       </c>
@@ -6438,7 +6822,9 @@
       <c r="C19" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="31" t="n"/>
+      <c r="D19" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="31" t="n">
         <v>4</v>
       </c>
@@ -6460,7 +6846,9 @@
       <c r="C20" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="31" t="n"/>
+      <c r="D20" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="31" t="n">
         <v>6</v>
       </c>
@@ -6482,7 +6870,9 @@
       <c r="C21" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="31" t="n"/>
+      <c r="D21" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="31" t="n">
         <v>6</v>
       </c>
@@ -6504,7 +6894,9 @@
       <c r="C22" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="31" t="n"/>
+      <c r="D22" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="31" t="n">
         <v>6</v>
       </c>
@@ -6526,7 +6918,9 @@
       <c r="C23" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="D23" s="31" t="n"/>
+      <c r="D23" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="31" t="n">
         <v>4</v>
       </c>
@@ -6548,7 +6942,9 @@
       <c r="C24" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="31" t="n"/>
+      <c r="D24" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="31" t="n">
         <v>3</v>
       </c>
@@ -6570,7 +6966,9 @@
       <c r="C25" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="31" t="n"/>
+      <c r="D25" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="31" t="n">
         <v>5</v>
       </c>
@@ -6592,7 +6990,9 @@
       <c r="C26" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="31" t="n"/>
+      <c r="D26" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="31" t="n">
         <v>9</v>
       </c>
@@ -6614,7 +7014,9 @@
       <c r="C27" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="31" t="n"/>
+      <c r="D27" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="31" t="n">
         <v>8</v>
       </c>
@@ -6636,7 +7038,9 @@
       <c r="C28" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="31" t="n"/>
+      <c r="D28" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="31" t="n">
         <v>9</v>
       </c>
@@ -6658,7 +7062,9 @@
       <c r="C29" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="31" t="n"/>
+      <c r="D29" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="31" t="n">
         <v>8</v>
       </c>
@@ -6680,7 +7086,9 @@
       <c r="C30" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="31" t="n"/>
+      <c r="D30" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="31" t="n">
         <v>9</v>
       </c>
@@ -6702,7 +7110,9 @@
       <c r="C31" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="D31" s="31" t="n"/>
+      <c r="D31" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="31" t="n">
         <v>9</v>
       </c>
@@ -6724,7 +7134,9 @@
       <c r="C32" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="D32" s="31" t="n"/>
+      <c r="D32" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="31" t="n">
         <v>10</v>
       </c>
@@ -6746,7 +7158,9 @@
       <c r="C33" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D33" s="31" t="n"/>
+      <c r="D33" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="31" t="n">
         <v>4</v>
       </c>
@@ -6768,7 +7182,9 @@
       <c r="C34" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D34" s="31" t="n"/>
+      <c r="D34" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="31" t="n">
         <v>4</v>
       </c>
@@ -6790,7 +7206,9 @@
       <c r="C35" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="31" t="n"/>
+      <c r="D35" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="31" t="n">
         <v>4</v>
       </c>
@@ -6812,7 +7230,9 @@
       <c r="C36" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D36" s="31" t="n"/>
+      <c r="D36" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="31" t="n">
         <v>3</v>
       </c>
@@ -6834,7 +7254,9 @@
       <c r="C37" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="31" t="n"/>
+      <c r="D37" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="31" t="n">
         <v>5</v>
       </c>
@@ -6856,7 +7278,9 @@
       <c r="C38" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="D38" s="31" t="n"/>
+      <c r="D38" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="31" t="n">
         <v>3</v>
       </c>
@@ -6878,7 +7302,9 @@
       <c r="C39" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="31" t="n"/>
+      <c r="D39" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="31" t="n">
         <v>5</v>
       </c>
@@ -7028,6 +7454,10 @@
           <t>SICIP required space for 30 trainees</t>
         </is>
       </c>
+      <c r="D7" s="24" t="n"/>
+      <c r="E7" s="24" t="n"/>
+      <c r="F7" s="24" t="n"/>
+      <c r="G7" s="25" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1" s="20">
       <c r="B8" s="37" t="inlineStr">
@@ -7043,6 +7473,10 @@
 Classroom cum workshop - 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="24" t="n"/>
+      <c r="E8" s="24" t="n"/>
+      <c r="F8" s="24" t="n"/>
+      <c r="G8" s="25" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="38" t="inlineStr">
@@ -7112,7 +7546,9 @@
       <c r="C16" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="44" t="n"/>
+      <c r="D16" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="44" t="n">
         <v>5</v>
       </c>
@@ -7134,7 +7570,9 @@
       <c r="C17" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="44" t="n"/>
+      <c r="D17" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="44" t="n">
         <v>5</v>
       </c>
@@ -7156,7 +7594,9 @@
       <c r="C18" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="44" t="n"/>
+      <c r="D18" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="44" t="n">
         <v>4</v>
       </c>
@@ -7178,7 +7618,9 @@
       <c r="C19" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="44" t="n"/>
+      <c r="D19" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="44" t="n">
         <v>4</v>
       </c>
@@ -7200,7 +7642,9 @@
       <c r="C20" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="44" t="n"/>
+      <c r="D20" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="44" t="n">
         <v>3</v>
       </c>
@@ -7222,7 +7666,9 @@
       <c r="C21" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="44" t="n"/>
+      <c r="D21" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="44" t="n">
         <v>6</v>
       </c>
@@ -7244,7 +7690,9 @@
       <c r="C22" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="44" t="n"/>
+      <c r="D22" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="44" t="n">
         <v>6</v>
       </c>
@@ -7266,7 +7714,9 @@
       <c r="C23" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="44" t="n"/>
+      <c r="D23" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="44" t="n">
         <v>7</v>
       </c>
@@ -7288,7 +7738,9 @@
       <c r="C24" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="44" t="n"/>
+      <c r="D24" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="44" t="n">
         <v>7</v>
       </c>
@@ -7310,7 +7762,9 @@
       <c r="C25" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="44" t="n"/>
+      <c r="D25" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="44" t="n">
         <v>7</v>
       </c>
@@ -7332,7 +7786,9 @@
       <c r="C26" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="44" t="n"/>
+      <c r="D26" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="44" t="n">
         <v>6</v>
       </c>
@@ -7354,7 +7810,9 @@
       <c r="C27" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="44" t="n"/>
+      <c r="D27" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="44" t="n">
         <v>6</v>
       </c>
@@ -7376,7 +7834,9 @@
       <c r="C28" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="44" t="n"/>
+      <c r="D28" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="44" t="n">
         <v>6</v>
       </c>
@@ -7398,7 +7858,9 @@
       <c r="C29" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="44" t="n"/>
+      <c r="D29" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="44" t="n">
         <v>7</v>
       </c>
@@ -7420,7 +7882,9 @@
       <c r="C30" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="44" t="n"/>
+      <c r="D30" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="44" t="n">
         <v>6</v>
       </c>
@@ -7442,7 +7906,9 @@
       <c r="C31" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="44" t="n"/>
+      <c r="D31" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="44" t="n">
         <v>6</v>
       </c>
@@ -7464,7 +7930,9 @@
       <c r="C32" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="44" t="n"/>
+      <c r="D32" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="44" t="n">
         <v>6</v>
       </c>
@@ -7486,7 +7954,9 @@
       <c r="C33" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="44" t="n"/>
+      <c r="D33" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="44" t="n">
         <v>6</v>
       </c>
@@ -7508,7 +7978,9 @@
       <c r="C34" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="44" t="n"/>
+      <c r="D34" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="44" t="n">
         <v>6</v>
       </c>
@@ -7530,7 +8002,9 @@
       <c r="C35" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="44" t="n"/>
+      <c r="D35" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="44" t="n">
         <v>6</v>
       </c>
@@ -7552,7 +8026,9 @@
       <c r="C36" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="44" t="n"/>
+      <c r="D36" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="44" t="n">
         <v>6</v>
       </c>
@@ -7574,7 +8050,9 @@
       <c r="C37" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="44" t="n"/>
+      <c r="D37" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="44" t="n">
         <v>6</v>
       </c>
@@ -7596,7 +8074,9 @@
       <c r="C38" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="44" t="n"/>
+      <c r="D38" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="44" t="n">
         <v>6</v>
       </c>
@@ -7618,7 +8098,9 @@
       <c r="C39" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="D39" s="44" t="n"/>
+      <c r="D39" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="44" t="n">
         <v>6</v>
       </c>
@@ -7640,7 +8122,9 @@
       <c r="C40" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D40" s="44" t="n"/>
+      <c r="D40" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="44" t="n">
         <v>7</v>
       </c>
@@ -7662,7 +8146,9 @@
       <c r="C41" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="D41" s="44" t="n"/>
+      <c r="D41" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="44" t="n">
         <v>6</v>
       </c>
@@ -7684,7 +8170,9 @@
       <c r="C42" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D42" s="44" t="n"/>
+      <c r="D42" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="44" t="n">
         <v>6</v>
       </c>
@@ -7706,7 +8194,9 @@
       <c r="C43" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D43" s="44" t="n"/>
+      <c r="D43" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" s="44" t="n">
         <v>5</v>
       </c>
@@ -7728,7 +8218,9 @@
       <c r="C44" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D44" s="44" t="n"/>
+      <c r="D44" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E44" s="44" t="n">
         <v>6</v>
       </c>
@@ -7750,7 +8242,9 @@
       <c r="C45" s="44" t="n">
         <v>15</v>
       </c>
-      <c r="D45" s="44" t="n"/>
+      <c r="D45" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E45" s="44" t="n">
         <v>4</v>
       </c>
@@ -7772,7 +8266,9 @@
       <c r="C46" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D46" s="44" t="n"/>
+      <c r="D46" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E46" s="44" t="n">
         <v>3</v>
       </c>
@@ -7794,7 +8290,9 @@
       <c r="C47" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="D47" s="44" t="n"/>
+      <c r="D47" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E47" s="44" t="n">
         <v>5</v>
       </c>
@@ -7816,7 +8314,9 @@
       <c r="C48" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D48" s="44" t="n"/>
+      <c r="D48" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E48" s="44" t="n">
         <v>8</v>
       </c>
@@ -7838,7 +8338,9 @@
       <c r="C49" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D49" s="44" t="n"/>
+      <c r="D49" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E49" s="44" t="n">
         <v>7</v>
       </c>
@@ -7860,7 +8362,9 @@
       <c r="C50" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D50" s="44" t="n"/>
+      <c r="D50" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E50" s="44" t="n">
         <v>8</v>
       </c>
@@ -7882,7 +8386,9 @@
       <c r="C51" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D51" s="44" t="n"/>
+      <c r="D51" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E51" s="44" t="n">
         <v>7</v>
       </c>
@@ -7904,7 +8410,9 @@
       <c r="C52" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="D52" s="44" t="n"/>
+      <c r="D52" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E52" s="44" t="n">
         <v>8</v>
       </c>
@@ -7926,7 +8434,9 @@
       <c r="C53" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="D53" s="44" t="n"/>
+      <c r="D53" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E53" s="44" t="n">
         <v>8</v>
       </c>
@@ -7948,7 +8458,9 @@
       <c r="C54" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="D54" s="44" t="n"/>
+      <c r="D54" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E54" s="44" t="n">
         <v>8</v>
       </c>
@@ -7970,7 +8482,9 @@
       <c r="C55" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D55" s="44" t="n"/>
+      <c r="D55" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E55" s="44" t="n">
         <v>4</v>
       </c>
@@ -7992,7 +8506,9 @@
       <c r="C56" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="D56" s="44" t="n"/>
+      <c r="D56" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E56" s="44" t="n">
         <v>4</v>
       </c>
@@ -8014,7 +8530,9 @@
       <c r="C57" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="D57" s="44" t="n"/>
+      <c r="D57" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E57" s="44" t="n">
         <v>4</v>
       </c>
@@ -8036,7 +8554,9 @@
       <c r="C58" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D58" s="44" t="n"/>
+      <c r="D58" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E58" s="44" t="n">
         <v>3</v>
       </c>
@@ -8058,7 +8578,9 @@
       <c r="C59" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D59" s="44" t="n"/>
+      <c r="D59" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E59" s="44" t="n">
         <v>4</v>
       </c>
@@ -8080,7 +8602,9 @@
       <c r="C60" s="44" t="n">
         <v>10</v>
       </c>
-      <c r="D60" s="44" t="n"/>
+      <c r="D60" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E60" s="44" t="n">
         <v>3</v>
       </c>
@@ -8102,7 +8626,9 @@
       <c r="C61" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D61" s="44" t="n"/>
+      <c r="D61" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E61" s="44" t="n">
         <v>5</v>
       </c>
@@ -8124,7 +8650,9 @@
       <c r="C62" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D62" s="44" t="n"/>
+      <c r="D62" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E62" s="44" t="n">
         <v>6</v>
       </c>
@@ -8146,7 +8674,9 @@
       <c r="C63" s="44" t="n">
         <v>25</v>
       </c>
-      <c r="D63" s="44" t="n"/>
+      <c r="D63" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E63" s="44" t="n">
         <v>5</v>
       </c>
@@ -8168,7 +8698,9 @@
       <c r="C64" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D64" s="44" t="n"/>
+      <c r="D64" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E64" s="44" t="n">
         <v>4</v>
       </c>
@@ -8190,7 +8722,9 @@
       <c r="C65" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="D65" s="44" t="n"/>
+      <c r="D65" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="E65" s="44" t="n">
         <v>5</v>
       </c>
